--- a/data/Opioid_Dataset_Cleaned.xlsx
+++ b/data/Opioid_Dataset_Cleaned.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>BDI 16.86 to 2.29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>F(3,24) = 81.38</t>
+          <t>F(3,18) = 9.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0005</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -850,13 +850,15 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>1</v>
@@ -1083,7 +1085,11 @@
       <c r="H3" t="n">
         <v>1.39</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SD = 13.8 (Control), 10.8 (Ketamine); 95% CI 9.9-24.4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>&lt;0.05</t>
@@ -1128,7 +1134,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1389,7 +1395,7 @@
         <v>100</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>1</v>
@@ -1880,7 +1886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>120 mg time to OST resumption = 22.5 h vs placebo 13.9 h (NS)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1893,7 +1899,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90%CI, 0.14 to 0.20 ms/ng/mL</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2415,7 +2421,11 @@
       <c r="H8" t="n">
         <v>3.86</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>chi-squared = 3.86</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>&lt;.05</t>
@@ -2533,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>

--- a/data/Opioid_Dataset_Cleaned.xlsx
+++ b/data/Opioid_Dataset_Cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV8"/>
+  <dimension ref="A1:BW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,70 +719,75 @@
       </c>
       <c r="BI1" t="inlineStr">
         <is>
+          <t>BaseStatusReportedYN</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
           <t>SafetyReported</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>AnyAEReported</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>NumDistinctAEs</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>NParticipantsWithAE</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>AE_denominator</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>ArmScope</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>WorstSeverity</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>text_source</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>text_format</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>PromptVersion</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>RubricVersion</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>SourcePDF</t>
         </is>
@@ -987,64 +992,69 @@
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr">
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW2" t="inlineStr">
         <is>
           <t>opioids/j.1749-6632.2000.tb05213.x.pdf</t>
         </is>
@@ -1255,68 +1265,73 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>opioids/Jovaisa et al.pdf</t>
         </is>
@@ -1525,68 +1540,73 @@
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW4" t="inlineStr">
         <is>
           <t>opioids/PIIS0740547202002751.pdf</t>
         </is>
@@ -1795,68 +1815,73 @@
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW5" t="inlineStr">
         <is>
           <t>opioids/02791072.2007.10399860.pdf</t>
         </is>
@@ -2061,68 +2086,73 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>Severe</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BV6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW6" t="inlineStr">
         <is>
           <t>opioids/Ascending_single_dose_double_blind_place.pdf</t>
         </is>
@@ -2131,12 +2161,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P.L. Prior 2014</t>
+          <t>Savage 1973</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P.L. Prior, &amp; Prior, S. L. (2014). Ibogaine effect on cocaine craving and use in dependent patients - a double-blind, placebo-controlled pilot study. Journal of Addiction and Therapy, 1(2), 1-4.</t>
+          <t>Savage, C., &amp; McCabe, O. L. (1973). Residential psychedelic (LSD) therapy for the narcotic addict: A controlled study. Archives of General Psychiatry, 28(6), 808-814.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2145,60 +2175,62 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2014</v>
+        <v>1973</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lower positive-urine (relapse) rate in the ibogaine group (corresponding to ~10% of the sample) vs the placebo group across the 24-week follow-up</t>
+          <t>25% vs 5% (9/36 vs 2/37) verified abstinent at 12-month follow-up</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>F (repeated-measures ANOVA, urine-positivity primary outcome)</t>
+          <t>Chi-squared</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.45</v>
+        <v>3.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>F(3,12) = 2.45</t>
+          <t>chi-squared = 3.86</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>&lt;.05</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -2207,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -2215,18 +2247,28 @@
       <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Severe</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>&lt;30</t>
+        </is>
+      </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>76</v>
+      </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Non-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="AE7" t="n">
@@ -2234,17 +2276,17 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Single 1800 mg oral encapsulated ibogaine (75% purity Tabernanthe iboga extract) vs placebo sugar-powder capsule; 72-hour inpatient cardiac monitoring, then biweekly outpatient follow-up to 24 weeks.</t>
+          <t>Single high-dose LSD session (300-450µg) after ~24 hours preparatory psychotherapy over 4-6 weeks residential halfway-house stay; one week post-session integration therapy.</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -2254,7 +2296,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -2282,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -2291,13 +2333,13 @@
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -2323,334 +2365,69 @@
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="inlineStr">
         <is>
+          <t>Not numbered</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>Mild</t>
-        </is>
-      </c>
       <c r="BP7" t="inlineStr">
         <is>
+          <t>Severe</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>markdown</t>
-        </is>
-      </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>opioids/Ibogaine_Effect_on_Cocaine_Craving_and_U.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Savage 1973</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Savage, C., &amp; McCabe, O. L. (1973). Residential psychedelic (LSD) therapy for the narcotic addict: A controlled study. Archives of General Psychiatry, 28(6), 808-814.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Opioid</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1973</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>25% vs 5% (9/36 vs 2/37) verified abstinent at 12-month follow-up</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Chi-squared</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>chi-squared = 3.86</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>&lt;.05</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Severe</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>&lt;30</t>
-        </is>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>76</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Single high-dose LSD session (300-450µg) after ~24 hours preparatory psychotherapy over 4-6 weeks residential halfway-house stay; one week post-session integration therapy.</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>Not numbered</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>psychedelic_arm</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>Severe</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>born-digital</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>claude-sonnet-5</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>v1.2</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-      <c r="BU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW7" t="inlineStr">
         <is>
           <t>opioids/archpsyc.1973.01750360040005.pdf</t>
         </is>
